--- a/01_data_model/01_code_lists/03_country_codes/input/countryISO.xlsx
+++ b/01_data_model/01_code_lists/03_country_codes/input/countryISO.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanniejo\Documents_local\01_dataplatform\002_DataModel\00_Code\04_codelists_countries\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanniejo\Documents_local\01_dataplatform\021_SVbevraging\01_code\01_data_model\01_code_lists\03_country_codes\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224F2974-4E52-42E9-9B0D-DAEE6B8DDE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/01_data_model/01_code_lists/03_country_codes/input/countryISO.xlsx
+++ b/01_data_model/01_code_lists/03_country_codes/input/countryISO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanniejo\Documents_local\01_dataplatform\021_SVbevraging\01_code\01_data_model\01_code_lists\03_country_codes\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224F2974-4E52-42E9-9B0D-DAEE6B8DDE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F54B0D-879D-4246-B754-D0E346BB3E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1973" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="1237">
   <si>
     <t>value2</t>
   </si>
@@ -3716,6 +3716,21 @@
   </si>
   <si>
     <t>SK1</t>
+  </si>
+  <si>
+    <t>UNKNOWN</t>
+  </si>
+  <si>
+    <t>Onbekend</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Inconnu</t>
+  </si>
+  <si>
+    <t>unknown</t>
   </si>
 </sst>
 </file>
@@ -4068,7 +4083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H282"/>
+  <dimension ref="A1:H283"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
@@ -11406,6 +11421,32 @@
         <v>334</v>
       </c>
     </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B283" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C283">
+        <v>99999</v>
+      </c>
+      <c r="D283" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E283" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F283" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G283" t="s">
+        <v>1236</v>
+      </c>
+      <c r="H283" t="s">
+        <v>1236</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H282">
     <sortCondition ref="A2:A282"/>
